--- a/LC-CNC-Component-Certifications.xlsx
+++ b/LC-CNC-Component-Certifications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-LC_CNC/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1564" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E64F937-8A65-43F6-8FAC-2005D1ACD5CF}"/>
+  <xr:revisionPtr revIDLastSave="1629" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B595451E-03E3-4869-AECA-D10E911A7A8C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="233">
   <si>
     <t>Item</t>
   </si>
@@ -732,6 +732,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pjrc.com/store/teensy41.html#tech </t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -741,18 +744,10 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -782,29 +777,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -827,13 +799,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
@@ -841,6 +806,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -877,12 +849,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -948,71 +921,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="fill"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="fill"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
-    <cellStyle name="Good" xfId="2" builtinId="26"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1295,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O107"/>
+  <dimension ref="A2:O107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -1309,407 +1262,448 @@
     <col min="22" max="22" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="8" t="s">
         <v>177</v>
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="1"/>
       <c r="G9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="1"/>
       <c r="G10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="1"/>
       <c r="G11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="1"/>
       <c r="G12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="1"/>
       <c r="G13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="1"/>
       <c r="G14" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="1"/>
       <c r="G15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>231</v>
       </c>
       <c r="G16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="1"/>
       <c r="G17" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="1" t="s">
         <v>189</v>
       </c>
       <c r="G19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="1" t="s">
         <v>187</v>
       </c>
       <c r="G21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="1" t="s">
         <v>191</v>
       </c>
       <c r="G22" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="1" t="s">
         <v>229</v>
       </c>
       <c r="G24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="1" t="s">
         <v>228</v>
       </c>
       <c r="G25" t="s">
@@ -1719,1115 +1713,1130 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="1" t="s">
         <v>227</v>
       </c>
       <c r="G26" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="1" t="s">
         <v>226</v>
       </c>
       <c r="G27" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="1" t="s">
         <v>225</v>
       </c>
       <c r="G28" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>232</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="1" t="s">
         <v>223</v>
       </c>
       <c r="G29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="G30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
       <c r="G31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
       <c r="G32" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
       <c r="G33" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
       <c r="G34" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
       <c r="G35" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
       <c r="G36" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
       <c r="G37" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
       <c r="G38" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
       <c r="G39" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
       <c r="G40" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
       <c r="G41" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
       <c r="G42" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
       <c r="G43" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
       <c r="G44" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="20"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="D46" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F46" s="4"/>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="20"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="D48" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="D49" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E50" s="4" t="s">
+      <c r="D50" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F50" s="4"/>
+      <c r="F50" s="1"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="D51" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F51" s="4"/>
+      <c r="F51" s="1"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="D52" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F52" s="4"/>
+      <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="D53" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F53" s="4"/>
+      <c r="F53" s="1"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="D54" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="4"/>
+      <c r="F54" s="1"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E55" s="4" t="s">
+      <c r="D55" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F55" s="4"/>
+      <c r="F55" s="1"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E56" s="4" t="s">
+      <c r="D56" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F56" s="4"/>
+      <c r="F56" s="1"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" s="4" t="s">
+      <c r="D57" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F57" s="4"/>
+      <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="D58" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F58" s="4"/>
+      <c r="F58" s="1"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E59" s="4" t="s">
+      <c r="D59" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F59" s="4"/>
+      <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F60" s="4"/>
+      <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E61" s="4" t="s">
+      <c r="D61" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F61" s="4"/>
+      <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="D62" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F62" s="4"/>
+      <c r="F62" s="1"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E63" s="4" t="s">
+      <c r="D63" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F63" s="4"/>
+      <c r="F63" s="1"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="D64" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F64" s="4"/>
+      <c r="F64" s="1"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E65" s="4" t="s">
+      <c r="D65" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F65" s="4"/>
+      <c r="F65" s="1"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E66" s="4" t="s">
+      <c r="D66" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F66" s="4"/>
+      <c r="F66" s="1"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="D67" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F67" s="4"/>
+      <c r="F67" s="1"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="D68" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F68" s="4"/>
+      <c r="F68" s="1"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="D69" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F69" s="4"/>
+      <c r="F69" s="1"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E70" s="4" t="s">
+      <c r="D70" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F70" s="4"/>
+      <c r="F70" s="1"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E71" s="28" t="s">
+      <c r="D71" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F71" s="4"/>
+      <c r="F71" s="1"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" s="4" t="s">
+      <c r="D72" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F72" s="4"/>
+      <c r="F72" s="1"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E73" s="4" t="s">
+      <c r="D73" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F73" s="4"/>
+      <c r="F73" s="1"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E74" s="4" t="s">
+      <c r="D74" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F74" s="4"/>
+      <c r="F74" s="1"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E75" s="4" t="s">
+      <c r="D75" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F75" s="4"/>
+      <c r="F75" s="1"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="D76" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F76" s="4"/>
+      <c r="F76" s="1"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E77" s="4" t="s">
+      <c r="D77" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F77" s="4"/>
+      <c r="F77" s="1"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="D78" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F78" s="4"/>
+      <c r="F78" s="1"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E79" s="4" t="s">
+      <c r="D79" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F79" s="4"/>
+      <c r="F79" s="1"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="D80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F80" s="4"/>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E81" s="4" t="s">
+      <c r="D81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F81" s="4"/>
-      <c r="J81" s="26"/>
+      <c r="F81" s="1"/>
+      <c r="J81" s="10"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E82" s="4" t="s">
+      <c r="D82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F82" s="4"/>
+      <c r="F82" s="1"/>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E83" s="4" t="s">
+      <c r="D83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F83" s="4"/>
+      <c r="F83" s="1"/>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E84" s="4" t="s">
+      <c r="D84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F84" s="4"/>
+      <c r="F84" s="1"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E85" s="4" t="s">
+      <c r="D85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F85" s="4"/>
+      <c r="F85" s="1"/>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E86" s="4" t="s">
+      <c r="D86" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F86" s="4"/>
+      <c r="F86" s="1"/>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E87" s="4" t="s">
+      <c r="D87" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F87" s="4"/>
+      <c r="F87" s="1"/>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E88" s="4" t="s">
+      <c r="D88" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F88" s="4"/>
+      <c r="F88" s="1"/>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="20"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="13"/>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D92" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D94" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C96" s="19"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="20"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="13"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D97" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="20"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="13"/>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E99" s="4" t="s">
+      <c r="D99" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F99" s="4"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G101" s="2"/>
@@ -2837,16 +2846,16 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B98:F98"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B98:F98"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
     <hyperlink ref="C23" r:id="rId2" xr:uid="{C0F4C0B5-36EF-43C3-B339-AACD5F5C72D4}"/>
@@ -2954,6 +2963,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
@@ -3166,7 +3184,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
@@ -3177,16 +3195,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30F3C9A4-0D35-4985-9741-8479EE24B4B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3205,7 +3222,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3214,12 +3231,4 @@
     <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/LC-CNC-Component-Certifications.xlsx
+++ b/LC-CNC-Component-Certifications.xlsx
@@ -2972,8 +2972,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
     <xsd:import namespace="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <xsd:element name="properties">
@@ -3204,22 +3204,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30F3C9A4-0D35-4985-9741-8479EE24B4B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C762532F-3022-40C6-9E45-0C9746EED902}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
